--- a/data/trans_orig/P04B3_1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61169</t>
+          <t>62190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113404</t>
+          <t>110808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59075</t>
+          <t>58044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96671</t>
+          <t>94842</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129717</t>
+          <t>127562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192360</t>
+          <t>189633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70593</t>
+          <t>71227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58038</t>
+          <t>58239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63857</t>
+          <t>65577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116658</t>
+          <t>117093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50314</t>
+          <t>51614</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107314</t>
+          <t>111082</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>25851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59143</t>
+          <t>60720</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87314</t>
+          <t>87834</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>154516</t>
+          <t>155111</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>158887</t>
+          <t>158307</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>226711</t>
+          <t>226249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131583</t>
+          <t>133981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178509</t>
+          <t>178898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>310035</t>
+          <t>303366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>393561</t>
+          <t>393247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97052</t>
+          <t>95523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>141784</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102055</t>
+          <t>104544</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>304565</t>
+          <t>311198</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>217662</t>
+          <t>218409</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>458707</t>
+          <t>432622</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34824</t>
+          <t>36921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68611</t>
+          <t>73163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72858</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80569</t>
+          <t>80206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133487</t>
+          <t>132773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52170</t>
+          <t>51303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95643</t>
+          <t>96744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52082</t>
+          <t>48351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105558</t>
+          <t>105158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115043</t>
+          <t>119297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187657</t>
+          <t>188287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>155762</t>
+          <t>152985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>208491</t>
+          <t>207475</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126683</t>
+          <t>122159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>252942</t>
+          <t>251186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>305478</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>440233</t>
+          <t>438019</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105983</t>
+          <t>106084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144656</t>
+          <t>144104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90474</t>
+          <t>89638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141946</t>
+          <t>142552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>210463</t>
+          <t>209421</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272981</t>
+          <t>272303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49955</t>
+          <t>50669</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>79621</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41210</t>
+          <t>41219</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69505</t>
+          <t>70122</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>98890</t>
+          <t>98321</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144037</t>
+          <t>142590</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71743</t>
+          <t>71251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109330</t>
+          <t>111481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70733</t>
+          <t>72686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113049</t>
+          <t>114914</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155231</t>
+          <t>152996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212817</t>
+          <t>211589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230781</t>
+          <t>232859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279586</t>
+          <t>281247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>286880</t>
+          <t>284997</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>386604</t>
+          <t>396101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>533245</t>
+          <t>535345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>654425</t>
+          <t>659111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66202</t>
+          <t>62990</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>200493</t>
+          <t>202943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>142063</t>
+          <t>140059</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>191160</t>
+          <t>188385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>174945</t>
+          <t>197297</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>375086</t>
+          <t>379189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39679</t>
+          <t>35263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>128011</t>
+          <t>126829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80436</t>
+          <t>78837</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112435</t>
+          <t>112847</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107438</t>
+          <t>118357</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>225712</t>
+          <t>229048</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40684</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>154272</t>
+          <t>157089</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>90436</t>
+          <t>91427</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>125750</t>
+          <t>128140</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>128226</t>
+          <t>132421</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>263378</t>
+          <t>264527</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>418768</t>
+          <t>416695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>742159</t>
+          <t>749748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>309361</t>
+          <t>310002</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>400885</t>
+          <t>404086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>749294</t>
+          <t>742663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1193571</t>
+          <t>1142724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123056</t>
+          <t>122065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>159504</t>
+          <t>159260</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126254</t>
+          <t>126058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>159007</t>
+          <t>157703</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>258902</t>
+          <t>259916</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>308008</t>
+          <t>307734</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54170</t>
+          <t>55011</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83751</t>
+          <t>83783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76218</t>
+          <t>76138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102447</t>
+          <t>101856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>138474</t>
+          <t>138204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178545</t>
+          <t>178862</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90399</t>
+          <t>89687</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125930</t>
+          <t>124980</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67302</t>
+          <t>67378</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92178</t>
+          <t>92904</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>164733</t>
+          <t>163660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>207189</t>
+          <t>207801</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>223679</t>
+          <t>224712</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>267691</t>
+          <t>268567</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>220421</t>
+          <t>219168</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>253857</t>
+          <t>252289</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>456304</t>
+          <t>452658</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>513353</t>
+          <t>509884</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>81628</t>
+          <t>84018</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>109990</t>
+          <t>110274</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41135</t>
+          <t>45009</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>150596</t>
+          <t>153590</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>105562</t>
+          <t>105598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>253201</t>
+          <t>252724</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45123</t>
+          <t>45058</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67326</t>
+          <t>66963</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21759</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>88165</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>60808</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>145649</t>
+          <t>146369</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>48066</t>
+          <t>48819</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>71893</t>
+          <t>72056</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26428</t>
+          <t>25851</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>93158</t>
+          <t>93839</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>63915</t>
+          <t>61216</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>156052</t>
+          <t>156650</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142972</t>
+          <t>142215</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>173204</t>
+          <t>173295</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>284009</t>
+          <t>283542</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>516371</t>
+          <t>512729</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>433856</t>
+          <t>431955</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>747123</t>
+          <t>744490</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>59758</t>
+          <t>58721</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>81223</t>
+          <t>80606</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>84383</t>
+          <t>84690</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>109780</t>
+          <t>108997</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>148953</t>
+          <t>150519</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>181628</t>
+          <t>182884</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>36249</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>56539</t>
+          <t>54550</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>52983</t>
+          <t>52336</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>73067</t>
+          <t>72628</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,47 +4307,47 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>107453</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>94362</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>121600</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
           <t>17,16%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>107453</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>93794</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>121390</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>61785</t>
+          <t>62133</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>65880</t>
+          <t>64940</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>88596</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>110115</t>
+          <t>111922</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>141092</t>
+          <t>144246</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>104419</t>
+          <t>104407</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>130869</t>
+          <t>129874</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>175728</t>
+          <t>177919</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>205280</t>
+          <t>205937</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>290281</t>
+          <t>287671</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>328412</t>
+          <t>327567</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>604346</t>
+          <t>588431</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>851570</t>
+          <t>845529</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>728939</t>
+          <t>725657</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1027691</t>
+          <t>1024724</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1453880</t>
+          <t>1443795</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1823570</t>
+          <t>1813152</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>330629</t>
+          <t>322515</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>468030</t>
+          <t>467180</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>376428</t>
+          <t>375967</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>511697</t>
+          <t>506125</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>765267</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>952842</t>
+          <t>954378</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>444993</t>
+          <t>436694</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>630534</t>
+          <t>628065</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>443065</t>
+          <t>453259</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>599033</t>
+          <t>602186</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>960290</t>
+          <t>945840</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1197337</t>
+          <t>1201885</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1550481</t>
+          <t>1557268</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2082784</t>
+          <t>2111323</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1692402</t>
+          <t>1699710</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2175886</t>
+          <t>2208275</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3319354</t>
+          <t>3302257</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4013669</t>
+          <t>4029371</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84434</t>
+          <t>103107</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>80085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110808</t>
+          <t>132342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>74807</t>
+          <t>91881</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58044</t>
+          <t>70993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94842</t>
+          <t>115296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>159241</t>
+          <t>194988</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127562</t>
+          <t>163312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189633</t>
+          <t>230502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>46648</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71227</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42078</t>
+          <t>56662</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>40405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58239</t>
+          <t>77968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>87792</t>
+          <t>103311</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65577</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117093</t>
+          <t>132083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76376</t>
+          <t>73586</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51614</t>
+          <t>50607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111082</t>
+          <t>100981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40976</t>
+          <t>47074</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60720</t>
+          <t>68891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>120660</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87834</t>
+          <t>89988</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155111</t>
+          <t>153651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>193464</t>
+          <t>184452</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>158307</t>
+          <t>153689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>226249</t>
+          <t>218299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>155338</t>
+          <t>166895</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>133981</t>
+          <t>141624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178898</t>
+          <t>195642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>348802</t>
+          <t>351346</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>303366</t>
+          <t>307346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>393247</t>
+          <t>392497</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118088</t>
+          <t>136235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95523</t>
+          <t>113268</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>141784</t>
+          <t>162180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>163331</t>
+          <t>115768</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104544</t>
+          <t>97166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>311198</t>
+          <t>136511</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281418</t>
+          <t>252003</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>218409</t>
+          <t>223185</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>432622</t>
+          <t>283784</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52090</t>
+          <t>60410</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>44109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73163</t>
+          <t>80622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55039</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>80823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>107129</t>
+          <t>125145</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80206</t>
+          <t>104429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132773</t>
+          <t>152118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71365</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51303</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96744</t>
+          <t>102392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82849</t>
+          <t>95054</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48351</t>
+          <t>78375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105158</t>
+          <t>115369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>154214</t>
+          <t>170989</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119297</t>
+          <t>145400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188287</t>
+          <t>208498</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>181839</t>
+          <t>202667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152985</t>
+          <t>174847</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>207475</t>
+          <t>233016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>210715</t>
+          <t>225201</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122159</t>
+          <t>201794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251186</t>
+          <t>251805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>392554</t>
+          <t>427868</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>305478</t>
+          <t>392387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>438019</t>
+          <t>465378</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935316</t>
+          <t>976005</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935316</t>
+          <t>976005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935316</t>
+          <t>976005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>123918</t>
+          <t>152366</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106084</t>
+          <t>130111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144104</t>
+          <t>173605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>122379</t>
+          <t>139769</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89638</t>
+          <t>121181</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142552</t>
+          <t>159414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>246298</t>
+          <t>292135</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>209421</t>
+          <t>263535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272303</t>
+          <t>322166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>77591</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50669</t>
+          <t>62289</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79621</t>
+          <t>97439</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55981</t>
+          <t>66704</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41219</t>
+          <t>54750</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70122</t>
+          <t>82088</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>121323</t>
+          <t>144295</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>98321</t>
+          <t>125598</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142590</t>
+          <t>166848</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89285</t>
+          <t>99787</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71251</t>
+          <t>80423</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111481</t>
+          <t>120976</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>95869</t>
+          <t>115380</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72686</t>
+          <t>98848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114914</t>
+          <t>132691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>185154</t>
+          <t>215167</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152996</t>
+          <t>190785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211589</t>
+          <t>243163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>256611</t>
+          <t>288936</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232859</t>
+          <t>263200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>281247</t>
+          <t>315850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>316882</t>
+          <t>299625</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>284997</t>
+          <t>279535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396101</t>
+          <t>321912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>573493</t>
+          <t>588561</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>535345</t>
+          <t>554801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>659111</t>
+          <t>621600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>535157</t>
+          <t>618680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>535157</t>
+          <t>618680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>535157</t>
+          <t>618680</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1126268</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1126268</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1126268</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>138972</t>
+          <t>160404</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62990</t>
+          <t>138483</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>202943</t>
+          <t>182755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>168107</t>
+          <t>186414</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>140059</t>
+          <t>168539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188385</t>
+          <t>207318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>307079</t>
+          <t>346818</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197297</t>
+          <t>316241</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>379189</t>
+          <t>376405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>86025</t>
+          <t>96008</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35263</t>
+          <t>78538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126829</t>
+          <t>116438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>97127</t>
+          <t>109920</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78837</t>
+          <t>95044</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112847</t>
+          <t>126019</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>183152</t>
+          <t>205927</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118357</t>
+          <t>184069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>229048</t>
+          <t>232019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>105872</t>
+          <t>115931</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>96368</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157089</t>
+          <t>138826</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>109491</t>
+          <t>117996</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91427</t>
+          <t>102174</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>128140</t>
+          <t>133694</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>215364</t>
+          <t>233928</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>132421</t>
+          <t>209017</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>264527</t>
+          <t>261853</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>556917</t>
+          <t>328274</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>416695</t>
+          <t>301714</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>749748</t>
+          <t>356230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>337500</t>
+          <t>321850</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310002</t>
+          <t>300142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>404086</t>
+          <t>342133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>894418</t>
+          <t>650124</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>742663</t>
+          <t>613031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1142724</t>
+          <t>684727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>712225</t>
+          <t>736180</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>712225</t>
+          <t>736180</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712225</t>
+          <t>736180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1600012</t>
+          <t>1436797</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1600012</t>
+          <t>1436797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1600012</t>
+          <t>1436797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140317</t>
+          <t>156002</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>122065</t>
+          <t>136172</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>159260</t>
+          <t>175203</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>143078</t>
+          <t>161137</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126058</t>
+          <t>144817</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>157703</t>
+          <t>179632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>283395</t>
+          <t>317139</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>259916</t>
+          <t>291534</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>307734</t>
+          <t>342847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>68115</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55011</t>
+          <t>60002</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83783</t>
+          <t>89400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>88984</t>
+          <t>102520</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76138</t>
+          <t>89433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101856</t>
+          <t>118185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>157099</t>
+          <t>176231</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>138204</t>
+          <t>155702</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178862</t>
+          <t>196670</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>106141</t>
+          <t>114634</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89687</t>
+          <t>96551</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124980</t>
+          <t>134094</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>79016</t>
+          <t>89793</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67378</t>
+          <t>77025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92904</t>
+          <t>103801</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>185157</t>
+          <t>204427</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>163660</t>
+          <t>182895</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>207801</t>
+          <t>230327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>246662</t>
+          <t>264999</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>224712</t>
+          <t>242522</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>268567</t>
+          <t>287659</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>236206</t>
+          <t>254698</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>219168</t>
+          <t>235848</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>252289</t>
+          <t>272938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>482868</t>
+          <t>519697</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>452658</t>
+          <t>490224</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>509884</t>
+          <t>547849</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1108519</t>
+          <t>1217494</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1108519</t>
+          <t>1217494</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1108519</t>
+          <t>1217494</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>96257</t>
+          <t>105240</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84018</t>
+          <t>91275</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110274</t>
+          <t>119286</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>97062</t>
+          <t>109083</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45009</t>
+          <t>95332</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>153590</t>
+          <t>120977</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>193318</t>
+          <t>214322</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>105598</t>
+          <t>194282</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>252724</t>
+          <t>234629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>62544</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45058</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66963</t>
+          <t>76039</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>55064</t>
+          <t>60537</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>51128</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88165</t>
+          <t>72559</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>110170</t>
+          <t>123081</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60808</t>
+          <t>107070</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>146369</t>
+          <t>142428</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>59487</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>53472</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>72056</t>
+          <t>80732</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>58727</t>
+          <t>63952</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>53920</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>93839</t>
+          <t>76163</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>130440</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>61216</t>
+          <t>113022</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>156650</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>157316</t>
+          <t>172809</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142215</t>
+          <t>156240</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>173295</t>
+          <t>190799</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>397515</t>
+          <t>205595</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>283542</t>
+          <t>192083</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>512729</t>
+          <t>220905</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>554831</t>
+          <t>378403</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>431955</t>
+          <t>354659</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>744490</t>
+          <t>400090</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>69997</t>
+          <t>77539</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58721</t>
+          <t>64855</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>80606</t>
+          <t>89471</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>95793</t>
+          <t>107756</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>84690</t>
+          <t>94682</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>108997</t>
+          <t>123024</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>165790</t>
+          <t>185295</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>150519</t>
+          <t>166257</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>182884</t>
+          <t>205058</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>44973</t>
+          <t>50782</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36249</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>54550</t>
+          <t>62602</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>62480</t>
+          <t>67547</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>52336</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>72628</t>
+          <t>79662</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>107453</t>
+          <t>118329</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>94362</t>
+          <t>103386</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>133759</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40100</t>
+          <t>43919</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>62133</t>
+          <t>67566</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>84792</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>73309</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>88596</t>
+          <t>97727</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>126960</t>
+          <t>140916</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>111922</t>
+          <t>123295</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>144246</t>
+          <t>157653</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>117185</t>
+          <t>125753</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>104407</t>
+          <t>112794</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>129874</t>
+          <t>140965</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>191203</t>
+          <t>204514</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>177919</t>
+          <t>189259</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>205937</t>
+          <t>220745</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>308387</t>
+          <t>330267</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>287671</t>
+          <t>309314</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>327567</t>
+          <t>354540</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>771982</t>
+          <t>890893</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>588431</t>
+          <t>835357</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>845529</t>
+          <t>945890</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>864557</t>
+          <t>911808</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>725657</t>
+          <t>867532</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1024724</t>
+          <t>962139</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1636539</t>
+          <t>1802701</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1443795</t>
+          <t>1729854</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1813152</t>
+          <t>1877262</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>417364</t>
+          <t>467694</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>322515</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>467180</t>
+          <t>514399</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>456754</t>
+          <t>528624</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>375967</t>
+          <t>492896</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>506125</t>
+          <t>573172</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>874117</t>
+          <t>996318</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>765267</t>
+          <t>947408</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>954378</t>
+          <t>1055853</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>559132</t>
+          <t>602486</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>436694</t>
+          <t>553874</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>628065</t>
+          <t>654311</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>543285</t>
+          <t>614041</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>453259</t>
+          <t>575851</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>602186</t>
+          <t>651834</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1102417</t>
+          <t>1216527</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>945840</t>
+          <t>1154464</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1201885</t>
+          <t>1281494</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1709993</t>
+          <t>1567890</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1557268</t>
+          <t>1507148</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2111323</t>
+          <t>1640260</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,67 +5082,67 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1845359</t>
+          <t>1678376</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1699710</t>
+          <t>1618982</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2208275</t>
+          <t>1734949</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>46,48%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>3246266</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>3163163</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>3326446</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
           <t>45,81%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>59,52%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>4031</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>3555352</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>3302257</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>4029371</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>49,6%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
